--- a/wiki/media/de/modul/m241/learningunits/lu02/theorie/m241_lb3_v1_bewertungsraster_pitch_video.xlsx
+++ b/wiki/media/de/modul/m241/learningunits/lu02/theorie/m241_lb3_v1_bewertungsraster_pitch_video.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bzzch-my.sharepoint.com/personal/volkan_demir_bzz_ch/Documents/--- Latest Version ---/WIKI-Importiert/M241/2_3_LB3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bzzch-my.sharepoint.com/personal/volkan_demir_bzz_ch/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{08DBB220-2F85-4C49-8FEC-F272EC3EEF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8620A78E-F473-433A-8507-40D0A1B82555}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{08DBB220-2F85-4C49-8FEC-F272EC3EEF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE60E938-2456-429A-B4F4-2C445EA9E16D}"/>
   <bookViews>
-    <workbookView xWindow="83295" yWindow="0" windowWidth="26010" windowHeight="20985" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TimeSlots" sheetId="16" r:id="rId1"/>
@@ -142,9 +142,6 @@
     <t>Namentliche Begrüssung des Stakeholders, dann die Klasse</t>
   </si>
   <si>
-    <t>Namentliche Verabschiedung des Stakeholders, dann die Klasse</t>
-  </si>
-  <si>
     <t>Baseline 3.5 Min.</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
     <t>Eingesetzte Pitch-Methode</t>
   </si>
   <si>
-    <t xml:space="preserve">Die Kernbotschaft des Pitches ist der Zuhöreraschaft wird addressatengerecht vermittelt. </t>
-  </si>
-  <si>
     <t>Der Zuhörer kann die Botschaft unmittelbar nach dem Pitch in einem Satz darlegen.Idealerweise direkt oder indirekt vom Presenter vorgegeben --&gt; Something catchy</t>
   </si>
   <si>
@@ -187,15 +181,9 @@
     <t>Wie gut sind die Präsentationsfähigkeiten des Vortragenden?</t>
   </si>
   <si>
-    <t>Bewertet werden Körpersprache, Augenkontakt und stimmlicher Überzeugungskraft, Zielführende Sprache?</t>
-  </si>
-  <si>
     <t>Standard ist Text: Stichwort + Fotos</t>
   </si>
   <si>
-    <t>Videos, Demos,Zitate, Geschichten, Dialoge, Show-Einlagen  sind zu zusätzlich.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wird das Marktpotenzial der Idee oder des Produkts überzeugend dargestellt? </t>
   </si>
   <si>
@@ -257,6 +245,18 @@
   </si>
   <si>
     <t>Schlechte Videoqualität: jeweils bis zu 10% für Bild und 10% für Ton.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Kernbotschaft des Pitches wird addressatengerecht vermittelt. </t>
+  </si>
+  <si>
+    <t>Wichtig: Man sieht die Hauptperson. Bewertet werden Körpersprache, Augenkontakt und stimmlicher Überzeugungskraft, zielführende Sprache.</t>
+  </si>
+  <si>
+    <t>Videos, Demos, Zitate, Geschichten, Dialoge, Show-Einlagen  sind zu zusätzlich.</t>
+  </si>
+  <si>
+    <t>Namentliche Verabschiedung des Stakeholders, dann die Klasse.</t>
   </si>
 </sst>
 </file>
@@ -816,11 +816,11 @@
     </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Eingabe" xfId="4" builtinId="20"/>
-    <cellStyle name="Gut" xfId="3" builtinId="26"/>
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Good" xfId="3" builtinId="26"/>
+    <cellStyle name="Input" xfId="4" builtinId="20"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
-    <cellStyle name="Schlecht" xfId="1" builtinId="27"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1099,7 +1099,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4AFEC3D-F927-4BD8-BB9F-676682983391}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="10.9453125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.20703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5234375" style="2" bestFit="1" customWidth="1"/>
@@ -1365,7 +1365,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5910A9CB-DF40-4223-8451-ECCF4D27A489}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="10.9453125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1374,7 +1374,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A40028FB-3471-485E-8043-8D7A61FF5BE2}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="10.9453125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1383,7 +1383,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1040E55D-EE25-44CD-BB43-38E49EA7925E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="10.9453125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1395,7 +1395,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.3125" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.68359375" style="4" customWidth="1"/>
@@ -1404,7 +1404,7 @@
     <col min="5" max="5" width="6.41796875" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.7890625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="54.68359375" style="8" customWidth="1"/>
-    <col min="8" max="8" width="62.89453125" style="6" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="62.89453125" style="6" customWidth="1"/>
     <col min="9" max="9" width="64.1015625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1444,7 +1444,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="41"/>
       <c r="D5" s="9">
@@ -1455,7 +1455,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="43"/>
       <c r="D6" s="47">
@@ -1509,10 +1509,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="38" t="s">
         <v>7</v>
@@ -1524,7 +1524,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1535,7 +1535,7 @@
         <v>17</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="29">
         <v>5</v>
@@ -1553,10 +1553,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D13" s="29">
         <v>3</v>
@@ -1572,10 +1572,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D14" s="29">
         <v>5</v>
@@ -1591,10 +1591,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D15" s="29">
         <v>2</v>
@@ -1610,10 +1610,10 @@
         <v>5</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" s="29">
         <v>3</v>
@@ -1622,7 +1622,7 @@
       <c r="F16" s="29"/>
       <c r="G16" s="28"/>
       <c r="H16" s="28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1665,7 +1665,7 @@
         <v>29</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D19" s="37">
         <v>2</v>
@@ -1686,7 +1686,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="D20" s="37">
         <v>5</v>
@@ -1695,7 +1695,7 @@
       <c r="F20" s="37"/>
       <c r="G20" s="36"/>
       <c r="H20" s="36" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1707,7 +1707,7 @@
         <v>28</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D21" s="37">
         <v>3</v>
@@ -1716,7 +1716,7 @@
       <c r="F21" s="37"/>
       <c r="G21" s="36"/>
       <c r="H21" s="36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1728,7 +1728,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D22" s="37">
         <v>5</v>
@@ -1737,10 +1737,10 @@
       <c r="F22" s="37"/>
       <c r="G22" s="36"/>
       <c r="H22" s="36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="5" customFormat="1" ht="30.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="31">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D23" s="37">
         <v>4</v>
@@ -1758,7 +1758,7 @@
       <c r="F23" s="37"/>
       <c r="G23" s="36"/>
       <c r="H23" s="36" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1770,7 +1770,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D24" s="37">
         <v>3</v>
@@ -1779,10 +1779,10 @@
       <c r="F24" s="37"/>
       <c r="G24" s="36"/>
       <c r="H24" s="36" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="5" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="5" customFormat="1" ht="44.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="31">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1800,7 +1800,7 @@
       <c r="F25" s="37"/>
       <c r="G25" s="36"/>
       <c r="H25" s="36" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1812,7 +1812,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D26" s="37">
         <v>4</v>
@@ -1821,7 +1821,7 @@
       <c r="F26" s="37"/>
       <c r="G26" s="36"/>
       <c r="H26" s="36" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -1830,10 +1830,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D27" s="37">
         <v>2</v>
@@ -1842,7 +1842,7 @@
       <c r="F27" s="37"/>
       <c r="G27" s="36"/>
       <c r="H27" s="36" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1876,10 +1876,10 @@
         <v>15</v>
       </c>
       <c r="B30" s="60" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D30" s="61">
         <f>-$D$10*0.1</f>
@@ -1896,10 +1896,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="60" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C31" s="60" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D31" s="61">
         <f>-$D$10*0.25</f>
@@ -1918,10 +1918,10 @@
         <v>17</v>
       </c>
       <c r="B32" s="60" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C32" s="60" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D32" s="61">
         <f>-$D$10*0.1</f>
@@ -1938,10 +1938,10 @@
         <v>18</v>
       </c>
       <c r="B33" s="60" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C33" s="60" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D33" s="61">
         <f>-$D$10*0.1</f>
@@ -1960,7 +1960,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BE821B-7631-4049-812B-4110FE3769B4}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.7890625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.7890625" style="4" bestFit="1" customWidth="1"/>
@@ -1980,7 +1980,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3285230-7CD0-42FF-95C4-04EA1391DA66}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.7890625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.7890625" style="4" bestFit="1" customWidth="1"/>
@@ -2000,7 +2000,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA299E0-AFED-47BA-B0BD-BB87CE68D8B9}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.7890625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.7890625" style="4" bestFit="1" customWidth="1"/>
@@ -2022,7 +2022,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C09D19D-1048-4E4B-BCC0-C6C8A7440BCA}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.7890625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.7890625" style="4" bestFit="1" customWidth="1"/>
@@ -2042,7 +2042,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE4E9E9-E966-46A8-B62A-2665ABA8F235}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.7890625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="61.1015625" style="4" customWidth="1"/>
@@ -2062,7 +2062,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C586AA1A-0054-4850-A104-9F916FB25F8C}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="10.9453125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2071,33 +2071,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32CACF77-2B05-4CFE-9811-F0B9281C434A}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="10.9453125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d005a70f-e9eb-482f-be8b-dc15414a6e72">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fcc0db23-895c-44d3-85c9-563d09dd4648" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010063EF91E59A045E49BE546A552D95CD85" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="fd9e4270de889ab13512e1cc61b74a6d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d005a70f-e9eb-482f-be8b-dc15414a6e72" xmlns:ns3="fcc0db23-895c-44d3-85c9-563d09dd4648" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="365f97db1c2ecf002afa5e058d0d42c1" ns2:_="" ns3:_="">
     <xsd:import namespace="d005a70f-e9eb-482f-be8b-dc15414a6e72"/>
@@ -2272,32 +2252,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EEF1BED-7943-4904-A0B0-60D65170A535}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="fcc0db23-895c-44d3-85c9-563d09dd4648"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d005a70f-e9eb-482f-be8b-dc15414a6e72"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E59318-8684-46B0-9F86-3030C19DE6B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d005a70f-e9eb-482f-be8b-dc15414a6e72">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fcc0db23-895c-44d3-85c9-563d09dd4648" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55C78BE2-5054-4AF5-B232-36A2B813703B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2314,4 +2289,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E59318-8684-46B0-9F86-3030C19DE6B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EEF1BED-7943-4904-A0B0-60D65170A535}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="fcc0db23-895c-44d3-85c9-563d09dd4648"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d005a70f-e9eb-482f-be8b-dc15414a6e72"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>